--- a/artfynd/A 14485-2026 artfynd.xlsx
+++ b/artfynd/A 14485-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121208270</v>
+        <v>121206938</v>
       </c>
       <c r="B2" t="n">
-        <v>92031</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Källsvedet, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574858</v>
+        <v>575113</v>
       </c>
       <c r="R2" t="n">
-        <v>6630312</v>
+        <v>6630348</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206421</v>
+        <v>121208270</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,27 +787,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575036</v>
+        <v>574858</v>
       </c>
       <c r="R3" t="n">
-        <v>6630495</v>
+        <v>6630312</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,6 +879,210 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121107165</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Källsvedet, norr om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>575016</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6630640</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121206421</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Källsvedet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>575036</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6630495</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14485-2026 artfynd.xlsx
+++ b/artfynd/A 14485-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206938</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121208270</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121107165</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,8 +1103,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206421</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>